--- a/Softime/Bug report.xlsx
+++ b/Softime/Bug report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uli\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CD5AF9-603A-4AE3-BEC7-3123E23B8195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E08C502-2D4D-43B1-8B17-20B8A13810ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{7A22CC4B-B266-4BC9-A644-54C8FC02B286}"/>
   </bookViews>
